--- a/model/Output_Budget/5. Prosumer percentage/Grid Search/Evaluation Metrics.xlsx
+++ b/model/Output_Budget/5. Prosumer percentage/Grid Search/Evaluation Metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailaub-my.sharepoint.com/personal/mo10_aub_edu_lb/Documents/3-Research/Elsa/Model 1/Github/Model-1/model/Output_Budget/5. Prosumer percentage/Grid Search/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_085DD5975251848E653490D641245E3FB48F8927" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C28D0DA-8745-4857-9C18-E9B5D052A227}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_085D1ADFD560F60E623554765816AEBBB639841B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F84671B9-C613-4F39-A938-75467CA695DE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Prosumer percentage</t>
   </si>
@@ -40,16 +40,28 @@
     <t>Household Surplus</t>
   </si>
   <si>
+    <t>60</t>
+  </si>
+  <si>
     <t>25</t>
   </si>
   <si>
+    <t>90</t>
+  </si>
+  <si>
     <t>100</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>50</t>
   </si>
   <si>
     <t>75</t>
+  </si>
+  <si>
+    <t>40</t>
   </si>
   <si>
     <t>0</t>
@@ -416,8 +428,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -444,19 +460,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.13</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C2">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="D2">
-        <v>0.1302026213376791</v>
+        <v>7.9592443686727021E-2</v>
       </c>
       <c r="E2">
-        <v>5.8270494322515368E-2</v>
+        <v>0.1001161193053302</v>
       </c>
       <c r="F2">
-        <v>8228880.6935279723</v>
+        <v>8343838.6029534619</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -464,19 +480,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="C3">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="D3">
-        <v>6.4032814343545866E-2</v>
+        <v>0.1302026213376791</v>
       </c>
       <c r="E3">
-        <v>0.51662998712898789</v>
+        <v>5.8270494322515368E-2</v>
       </c>
       <c r="F3">
-        <v>6547303.0462612938</v>
+        <v>8228880.6935279723</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -490,13 +506,13 @@
         <v>0.34</v>
       </c>
       <c r="D4">
-        <v>9.5770197691731118E-2</v>
+        <v>5.3861149367329872E-2</v>
       </c>
       <c r="E4">
-        <v>0.1398172478970911</v>
+        <v>0.44513205670510358</v>
       </c>
       <c r="F4">
-        <v>8417063.6393414065</v>
+        <v>7072240.9492407991</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -510,26 +526,106 @@
         <v>0.32</v>
       </c>
       <c r="D5">
-        <v>8.6158966989845265E-2</v>
+        <v>6.4032814343545866E-2</v>
       </c>
       <c r="E5">
-        <v>0.26619488180934903</v>
+        <v>0.51662998712898789</v>
       </c>
       <c r="F5">
-        <v>7745438.9772295002</v>
+        <v>6547303.0462612938</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B6">
+        <v>0.17</v>
+      </c>
       <c r="C6">
+        <v>0.38</v>
+      </c>
+      <c r="D6">
+        <v>0.171525950819475</v>
+      </c>
+      <c r="E6">
+        <v>8.0008600495539678E-2</v>
+      </c>
+      <c r="F6">
+        <v>7873987.9189035706</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>0.1</v>
+      </c>
+      <c r="C7">
+        <v>0.34</v>
+      </c>
+      <c r="D7">
+        <v>9.5770197691731118E-2</v>
+      </c>
+      <c r="E7">
+        <v>0.1398172478970911</v>
+      </c>
+      <c r="F7">
+        <v>8417063.6393414065</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>0.08</v>
+      </c>
+      <c r="C8">
+        <v>0.32</v>
+      </c>
+      <c r="D8">
+        <v>8.6158966989845265E-2</v>
+      </c>
+      <c r="E8">
+        <v>0.26619488180934903</v>
+      </c>
+      <c r="F8">
+        <v>7745438.9772295002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>0.11</v>
+      </c>
+      <c r="C9">
+        <v>0.35</v>
+      </c>
+      <c r="D9">
+        <v>0.11574524252798921</v>
+      </c>
+      <c r="E9">
+        <v>0.10138619668873269</v>
+      </c>
+      <c r="F9">
+        <v>8393080.9751948956</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
         <v>0.39</v>
       </c>
-      <c r="D6">
+      <c r="D10">
         <v>0.1748909501816468</v>
       </c>
-      <c r="F6">
+      <c r="F10">
         <v>7627398.21940412</v>
       </c>
     </row>
